--- a/data/tags/סינגלים חדשים/global/2026-02-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יערה טופ – Kill Me</v>
+        <v>ששון שאולוב - מלי מלי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-22</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%a2%d7%a8%d7%94-%d7%98%d7%95%d7%a4-kill-me/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409712&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-22</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>יערה טופ שרה בלדת פולק אקוסטית עדינה, כמעט חשופה, שמצליחה להחזיק בתוכה טקסט טעון  על תשוקה, תלות, ופחד מאינטימיות. למרות הכותרת הדרמטית, זה אינו שיר על מוות כפשוטו, אלא על הסכמה להיעלם בתוך אהבה ועל הסכנה שבכך. ה”Kill me” היא</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יערה טופ – Kill Me</v>
+        <v>ששון שאולוב - מלי מלי</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אלדד ציטרין וגלי עטרי – רק במנגינה</v>
+        <v>שי וינר - תן לי</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-22</v>
       </c>
       <c r="C3" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%9c%d7%93%d7%93-%d7%a6%d7%99%d7%98%d7%a8%d7%99%d7%9f-%d7%95%d7%92%d7%9c%d7%99-%d7%a2%d7%98%d7%a8%d7%99-%d7%a8%d7%a7-%d7%91%d7%9e%d7%a0%d7%92%d7%99%d7%a0%d7%94/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409711&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-22</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>זהו שיר שקט, מינימליסטי, מעודן, תואם את גוון שירתה של גלי עטרי. בתוכו מתקיים דיאלוג על ערך עצמי אחרי פרידה. לא מדובר בשיר אהבה, אלא בשיר על תיקון חלקי. הוא נפתח בשאלות: “מי לך אמר את לא מיוחדת מי לך</v>
+        <v/>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -507,12 +507,316 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אלדד ציטרין וגלי עטרי – רק במנגינה</v>
+        <v>שי וינר - תן לי</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>עדן גולן - מספיק ממך</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-02-22</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409710&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-02-22</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>עדן גולן - מספיק ממך</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>סטטיק - מנדם</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-02-22</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409709&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-02-22</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>סטטיק - מנדם</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>נעומי טוב אלמליח - מעבר לדמיון</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-02-22</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409708&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-02-22</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>נעומי טוב אלמליח - מעבר לדמיון</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>יגל יובל שרעבי - מחושך לאור</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-02-22</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409707&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-02-22</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>יגל יובל שרעבי - מחושך לאור</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>ויולט - לנוע</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-02-22</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409706&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-02-22</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>ויולט - לנוע</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>דניאלה גלבוע - איפה שהכל נגמר</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-02-22</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409705&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-02-22</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>דניאלה גלבוע - איפה שהכל נגמר</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>אלמוג זגרון - ג׳ורדן</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-02-22</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409704&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-02-22</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>אלמוג זגרון - ג׳ורדן</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אדיר בובליל - בא לי שוב</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-02-22</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409703&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-02-22</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אדיר בובליל - בא לי שוב</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-02-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ששון שאולוב - מלי מלי</v>
+        <v>קרן קריספיל - עד שמצאתי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-22</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409712&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409722&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ששון שאולוב - מלי מלי</v>
+        <v>קרן קריספיל - עד שמצאתי</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>שי וינר - תן לי</v>
+        <v>סער הדר - טוב לך איתו</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-22</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409711&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409721&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>שי וינר - תן לי</v>
+        <v>סער הדר - טוב לך איתו</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>עדן גולן - מספיק ממך</v>
+        <v>ים רפאלי - ערפדים</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-22</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409710&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409720&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>עדן גולן - מספיק ממך</v>
+        <v>ים רפאלי - ערפדים</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>סטטיק - מנדם</v>
+        <v>טל קייסי - בלב הסערה</v>
       </c>
       <c r="B5" t="str">
         <v>2026-02-22</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409709&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409719&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>סטטיק - מנדם</v>
+        <v>טל קייסי - בלב הסערה</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>נעומי טוב אלמליח - מעבר לדמיון</v>
+        <v>אלי בי - רק תני לי סימן</v>
       </c>
       <c r="B6" t="str">
         <v>2026-02-22</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409708&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409718&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>נעומי טוב אלמליח - מעבר לדמיון</v>
+        <v>אלי בי - רק תני לי סימן</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>יגל יובל שרעבי - מחושך לאור</v>
+        <v>איתי אהרון - אהבה כאב וטעויות</v>
       </c>
       <c r="B7" t="str">
         <v>2026-02-22</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409707&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409717&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>יגל יובל שרעבי - מחושך לאור</v>
+        <v>איתי אהרון - אהבה כאב וטעויות</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ויולט - לנוע</v>
+        <v>אייל לוי - מדויק</v>
       </c>
       <c r="B8" t="str">
         <v>2026-02-22</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409706&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409716&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>ויולט - לנוע</v>
+        <v>אייל לוי - מדויק</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>דניאלה גלבוע - איפה שהכל נגמר</v>
+        <v>אחי נתן - לא בחור דתי</v>
       </c>
       <c r="B9" t="str">
         <v>2026-02-22</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409705&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409715&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>דניאלה גלבוע - איפה שהכל נגמר</v>
+        <v>אחי נתן - לא בחור דתי</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>אלמוג זגרון - ג׳ורדן</v>
+        <v>אורן כדורי - למה ככה</v>
       </c>
       <c r="B10" t="str">
         <v>2026-02-22</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409704&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409714&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -773,21 +773,21 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>אלמוג זגרון - ג׳ורדן</v>
+        <v>אורן כדורי - למה ככה</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>אדיר בובליל - בא לי שוב</v>
+        <v>אייל שלום - אתה חי</v>
       </c>
       <c r="B11" t="str">
         <v>2026-02-22</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409703&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409713&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -811,12 +811,50 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>אדיר בובליל - בא לי שוב</v>
+        <v>אייל שלום - אתה חי</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Garden City Movement – I Can Be Your Salvation</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-02-23</v>
+      </c>
+      <c r="C12" t="str">
+        <v>https://yosmusic.com/garden-city-movement/</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-02-23</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v>בלב המוזיקה האוורירית-אלקטרונית של הצמד יוני שרוני  ורועי אביטל המהווים  את Garden City Movement מסתתר טקסט לא רגוע בכלל. זוהי מוסיקה ריחופית שמדברת על שליטה, בלבול ותלות רגשית בעידן של עודף גירויים. השורה הראשונה מציבה את הדילמה: “?Could you choose</v>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>Garden City Movement – I Can Be Your Salvation</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-02-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>קרן קריספיל - עד שמצאתי</v>
+        <v>מירי מסיקה – גידי</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409722&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
+        <v>https://yosmusic.com/%d7%9e%d7%99%d7%a8%d7%99-%d7%9e%d7%a1%d7%99%d7%a7%d7%94-%d7%92%d7%99%d7%93%d7%99/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-23</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>"גידי” הוא שיר פופ דרמטי של שרון ליפשיץ משנות ה־80 שמגלם נשיות תיאטרלית, הנמצאת בסיטואציה של אהבה תלויה.החידוש של מירי מסיקה (במסגרת הסדרה "ריסט") לוקח את אותו טקסט טעון  ומלביש עליו אסתטיקה אלקטרונית עדכנית עם גרוב פאנקי ובס מודגש, מה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,392 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>קרן קריספיל - עד שמצאתי</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>סער הדר - טוב לך איתו</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-02-22</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409721&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-02-23</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>סער הדר - טוב לך איתו</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>ים רפאלי - ערפדים</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-02-22</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409720&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-02-23</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>ים רפאלי - ערפדים</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>טל קייסי - בלב הסערה</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-02-22</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409719&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-02-23</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>טל קייסי - בלב הסערה</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>אלי בי - רק תני לי סימן</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-02-22</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409718&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-02-23</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>אלי בי - רק תני לי סימן</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>איתי אהרון - אהבה כאב וטעויות</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-02-22</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409717&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-02-23</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>איתי אהרון - אהבה כאב וטעויות</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>אייל לוי - מדויק</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-02-22</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409716&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-02-23</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>אייל לוי - מדויק</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>אחי נתן - לא בחור דתי</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-02-22</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409715&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-02-23</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>אחי נתן - לא בחור דתי</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>אורן כדורי - למה ככה</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-02-22</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409714&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-02-23</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>אורן כדורי - למה ככה</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>אייל שלום - אתה חי</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-02-22</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409713&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-02-23</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>אייל שלום - אתה חי</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Garden City Movement – I Can Be Your Salvation</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-02-23</v>
-      </c>
-      <c r="C12" t="str">
-        <v>https://yosmusic.com/garden-city-movement/</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-02-23</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v>בלב המוזיקה האוורירית-אלקטרונית של הצמד יוני שרוני  ורועי אביטל המהווים  את Garden City Movement מסתתר טקסט לא רגוע בכלל. זוהי מוסיקה ריחופית שמדברת על שליטה, בלבול ותלות רגשית בעידן של עודף גירויים. השורה הראשונה מציבה את הדילמה: “?Could you choose</v>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>Garden City Movement – I Can Be Your Salvation</v>
+        <v>מירי מסיקה – גידי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-02-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מירי מסיקה – גידי</v>
+        <v>בר צברי – ראש לאריות</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-23</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%99%d7%a8%d7%99-%d7%9e%d7%a1%d7%99%d7%a7%d7%94-%d7%92%d7%99%d7%93%d7%99/</v>
+        <v>https://yosmusic.com/%d7%91%d7%a8-%d7%a6%d7%91%d7%a8%d7%99-%d7%a8%d7%90%d7%a9-%d7%9c%d7%90%d7%a8%d7%99%d7%95%d7%aa/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-23</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"גידי” הוא שיר פופ דרמטי של שרון ליפשיץ משנות ה־80 שמגלם נשיות תיאטרלית, הנמצאת בסיטואציה של אהבה תלויה.החידוש של מירי מסיקה (במסגרת הסדרה "ריסט") לוקח את אותו טקסט טעון  ומלביש עליו אסתטיקה אלקטרונית עדכנית עם גרוב פאנקי ובס מודגש, מה</v>
+        <v>השיר "ראש לאריות" של בר צברי נכתב לזכרו של לוחם הימ״מ ארנון זמורה ז״ל, שנהרג במבצע חילוץ בעזה במהלך מלחמת חרבות ברזל. זוהי בלדה אישית ואינטימית שהופכת מדמות פרטית – אדם, אב ובעל – לסמל של גבורה ישראלית. כבר מן</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מירי מסיקה – גידי</v>
+        <v>בר צברי – ראש לאריות</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-02-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>בר צברי – ראש לאריות</v>
+        <v>חיים איפרגן - אשרף טק</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-23</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%91%d7%a8-%d7%a6%d7%91%d7%a8%d7%99-%d7%a8%d7%90%d7%a9-%d7%9c%d7%90%d7%a8%d7%99%d7%95%d7%aa/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409731&amp;sid=b7524068d0c67c249ff82f0b4d80f8bb</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-23</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "ראש לאריות" של בר צברי נכתב לזכרו של לוחם הימ״מ ארנון זמורה ז״ל, שנהרג במבצע חילוץ בעזה במהלך מלחמת חרבות ברזל. זוהי בלדה אישית ואינטימית שהופכת מדמות פרטית – אדם, אב ובעל – לסמל של גבורה ישראלית. כבר מן</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,354 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>בר צברי – ראש לאריות</v>
+        <v>חיים איפרגן - אשרף טק</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>דוריה חממי - טעויות מהעבר</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-02-23</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409730&amp;sid=b7524068d0c67c249ff82f0b4d80f8bb</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-02-23</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>דוריה חממי - טעויות מהעבר</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>בר צברי - ראש לאריות</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-02-23</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409729&amp;sid=b7524068d0c67c249ff82f0b4d80f8bb</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-02-23</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>בר צברי - ראש לאריות</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>בן אל תבורי &amp; דנה אינטרנשיונל &amp; אמיר שורוש - מה עושים בלילות</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-02-23</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409728&amp;sid=b7524068d0c67c249ff82f0b4d80f8bb</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-02-23</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>בן אל תבורי &amp; דנה אינטרנשיונל &amp; אמיר שורוש - מה עושים בלילות</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>אמיר ישראל - מי עושה קפה</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-02-23</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409727&amp;sid=b7524068d0c67c249ff82f0b4d80f8bb</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-02-23</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>אמיר ישראל - מי עושה קפה</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>אייל ישי - לא דיברנו שנינו</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-02-23</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409726&amp;sid=b7524068d0c67c249ff82f0b4d80f8bb</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-02-23</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>אייל ישי - לא דיברנו שנינו</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>אוראל מנצור - מחרוזת נועצת מבט 2026</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-02-23</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409725&amp;sid=b7524068d0c67c249ff82f0b4d80f8bb</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-02-23</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>אוראל מנצור - מחרוזת נועצת מבט 2026</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אבי ביטר - מחרוזת לב פצוע 2026</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-02-23</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409724&amp;sid=b7524068d0c67c249ff82f0b4d80f8bb</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-02-23</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אבי ביטר - מחרוזת לב פצוע 2026</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>הפרויקט של תמרי ואהוד בנאי – יוצא לאור</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-02-23</v>
+      </c>
+      <c r="C10" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%aa%d7%9e%d7%a8%d7%99-%d7%95%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%99%d7%95%d7%a6%d7%90-%d7%9c%d7%90%d7%95%d7%a8/</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-02-23</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v>חוזרים לשביל של אהוד בנאי עם "הפרויקט של תמרי" בשיתוף היוצר. השביל הזה מתחיל מכאן, כלומר – מהמקום בו אתה עומד – מתחיל שביל שמוליך אל דבר לא ברור, אל אותו דבר שאתה רוצה לעשות, אבל אתה לא יודע איך"…</v>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>הפרויקט של תמרי ואהוד בנאי – יוצא לאור</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אייל אבן צור – פסל</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-02-23</v>
+      </c>
+      <c r="C11" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%99%d7%99%d7%9c-%d7%90%d7%91%d7%9f-%d7%a6%d7%95%d7%a8-%d7%a4%d7%a1%d7%9c/</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-02-23</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v>השיר "פסל" של אייל אבן צור הוא יצירה אינטימית ועדינה, שנשענת על עיבוד פופ־פולק מלודי בעל אווירה מלנכולית מאופקת. הביצוע בטון גבוה ומתכוון יוצר תחושת פגיעות – קול שנשמע כבוי במידה מסוימת, אך לא נשבר. יש בו המשכיות מתכוונת, כמו</v>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אייל אבן צור – פסל</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-02-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>חיים איפרגן - אשרף טק</v>
+        <v>תאיר מרציאנו - מחרוזת שקטים 2026</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-23</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409731&amp;sid=b7524068d0c67c249ff82f0b4d80f8bb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409739&amp;sid=7af29e71c4331da88b3f2f7ca7e09df9</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>חיים איפרגן - אשרף טק</v>
+        <v>תאיר מרציאנו - מחרוזת שקטים 2026</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>דוריה חממי - טעויות מהעבר</v>
+        <v>מרדכי רוט - שורף ובועט</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-23</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409730&amp;sid=b7524068d0c67c249ff82f0b4d80f8bb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409738&amp;sid=7af29e71c4331da88b3f2f7ca7e09df9</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>דוריה חממי - טעויות מהעבר</v>
+        <v>מרדכי רוט - שורף ובועט</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>בר צברי - ראש לאריות</v>
+        <v>מירי מסיקה - גידי</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-23</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409729&amp;sid=b7524068d0c67c249ff82f0b4d80f8bb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409737&amp;sid=7af29e71c4331da88b3f2f7ca7e09df9</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>בר צברי - ראש לאריות</v>
+        <v>מירי מסיקה - גידי</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>בן אל תבורי &amp; דנה אינטרנשיונל &amp; אמיר שורוש - מה עושים בלילות</v>
+        <v>מור מזרחי - מחרוזת דוקטור תציל אותי 2026</v>
       </c>
       <c r="B5" t="str">
         <v>2026-02-23</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409728&amp;sid=b7524068d0c67c249ff82f0b4d80f8bb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409736&amp;sid=7af29e71c4331da88b3f2f7ca7e09df9</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>בן אל תבורי &amp; דנה אינטרנשיונל &amp; אמיר שורוש - מה עושים בלילות</v>
+        <v>מור מזרחי - מחרוזת דוקטור תציל אותי 2026</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>אמיר ישראל - מי עושה קפה</v>
+        <v>יניב נסימי - מחרוזת חוזר אל הלב 2026</v>
       </c>
       <c r="B6" t="str">
         <v>2026-02-23</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409727&amp;sid=b7524068d0c67c249ff82f0b4d80f8bb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409735&amp;sid=7af29e71c4331da88b3f2f7ca7e09df9</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>אמיר ישראל - מי עושה קפה</v>
+        <v>יניב נסימי - מחרוזת חוזר אל הלב 2026</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>אייל ישי - לא דיברנו שנינו</v>
+        <v>יותם ששוני - ירח בחלון</v>
       </c>
       <c r="B7" t="str">
         <v>2026-02-23</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409726&amp;sid=b7524068d0c67c249ff82f0b4d80f8bb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409734&amp;sid=7af29e71c4331da88b3f2f7ca7e09df9</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>אייל ישי - לא דיברנו שנינו</v>
+        <v>יותם ששוני - ירח בחלון</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>אוראל מנצור - מחרוזת נועצת מבט 2026</v>
+        <v>יוסף שושן - בוחרת בעצמי</v>
       </c>
       <c r="B8" t="str">
         <v>2026-02-23</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409725&amp;sid=b7524068d0c67c249ff82f0b4d80f8bb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409733&amp;sid=7af29e71c4331da88b3f2f7ca7e09df9</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>אוראל מנצור - מחרוזת נועצת מבט 2026</v>
+        <v>יוסף שושן - בוחרת בעצמי</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אבי ביטר - מחרוזת לב פצוע 2026</v>
+        <v>חן ביטון - רבי נחמן אמר</v>
       </c>
       <c r="B9" t="str">
         <v>2026-02-23</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409724&amp;sid=b7524068d0c67c249ff82f0b4d80f8bb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409732&amp;sid=7af29e71c4331da88b3f2f7ca7e09df9</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,88 +735,12 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>אבי ביטר - מחרוזת לב פצוע 2026</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>הפרויקט של תמרי ואהוד בנאי – יוצא לאור</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-02-23</v>
-      </c>
-      <c r="C10" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%aa%d7%9e%d7%a8%d7%99-%d7%95%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%99%d7%95%d7%a6%d7%90-%d7%9c%d7%90%d7%95%d7%a8/</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-02-23</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v>חוזרים לשביל של אהוד בנאי עם "הפרויקט של תמרי" בשיתוף היוצר. השביל הזה מתחיל מכאן, כלומר – מהמקום בו אתה עומד – מתחיל שביל שמוליך אל דבר לא ברור, אל אותו דבר שאתה רוצה לעשות, אבל אתה לא יודע איך"…</v>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>הפרויקט של תמרי ואהוד בנאי – יוצא לאור</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>אייל אבן צור – פסל</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-02-23</v>
-      </c>
-      <c r="C11" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%99%d7%99%d7%9c-%d7%90%d7%91%d7%9f-%d7%a6%d7%95%d7%a8-%d7%a4%d7%a1%d7%9c/</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-02-23</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v>השיר "פסל" של אייל אבן צור הוא יצירה אינטימית ועדינה, שנשענת על עיבוד פופ־פולק מלודי בעל אווירה מלנכולית מאופקת. הביצוע בטון גבוה ומתכוון יוצר תחושת פגיעות – קול שנשמע כבוי במידה מסוימת, אך לא נשבר. יש בו המשכיות מתכוונת, כמו</v>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>אייל אבן צור – פסל</v>
+        <v>חן ביטון - רבי נחמן אמר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-02-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>תאיר מרציאנו - מחרוזת שקטים 2026</v>
+        <v>טוהר קדוש – סוף פואטי</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409739&amp;sid=7af29e71c4331da88b3f2f7ca7e09df9</v>
+        <v>https://yosmusic.com/%d7%98%d7%95%d7%94%d7%a8-%d7%a7%d7%93%d7%95%d7%a9-%d7%a1%d7%95%d7%a3-%d7%a4%d7%95%d7%90%d7%98%d7%99/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-24</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>השיר "סוף פואטי" של טוהר קדוש הוא בלדה אפלה על אחיזה נואשת באהבה שכבר איננה  דרך טקסים, פנטזיות ופולחן רגשי. העיבוד האלקטרוני העדין, בקצב מיד־טמפו איטי, יוצר תחושת לופ מתמשך גם מוזיקלית וגם נפשית. זו לא דרמה מתפרצת, אלא שחיקה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,278 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>תאיר מרציאנו - מחרוזת שקטים 2026</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>מרדכי רוט - שורף ובועט</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-02-23</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409738&amp;sid=7af29e71c4331da88b3f2f7ca7e09df9</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-02-24</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>מרדכי רוט - שורף ובועט</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>מירי מסיקה - גידי</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-02-23</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409737&amp;sid=7af29e71c4331da88b3f2f7ca7e09df9</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-02-24</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>מירי מסיקה - גידי</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>מור מזרחי - מחרוזת דוקטור תציל אותי 2026</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-02-23</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409736&amp;sid=7af29e71c4331da88b3f2f7ca7e09df9</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-02-24</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>מור מזרחי - מחרוזת דוקטור תציל אותי 2026</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>יניב נסימי - מחרוזת חוזר אל הלב 2026</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-02-23</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409735&amp;sid=7af29e71c4331da88b3f2f7ca7e09df9</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-02-24</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>יניב נסימי - מחרוזת חוזר אל הלב 2026</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>יותם ששוני - ירח בחלון</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-02-23</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409734&amp;sid=7af29e71c4331da88b3f2f7ca7e09df9</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-02-24</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>יותם ששוני - ירח בחלון</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>יוסף שושן - בוחרת בעצמי</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-02-23</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409733&amp;sid=7af29e71c4331da88b3f2f7ca7e09df9</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-02-24</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>יוסף שושן - בוחרת בעצמי</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>חן ביטון - רבי נחמן אמר</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-02-23</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409732&amp;sid=7af29e71c4331da88b3f2f7ca7e09df9</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-02-24</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>חן ביטון - רבי נחמן אמר</v>
+        <v>טוהר קדוש – סוף פואטי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-02-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>טוהר קדוש – סוף פואטי</v>
+        <v>נדב דלומי – מאיר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-24</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%95%d7%94%d7%a8-%d7%a7%d7%93%d7%95%d7%a9-%d7%a1%d7%95%d7%a3-%d7%a4%d7%95%d7%90%d7%98%d7%99/</v>
+        <v>https://yosmusic.com/%d7%a0%d7%93%d7%91-%d7%93%d7%9c%d7%95%d7%9e%d7%99-%d7%9e%d7%90%d7%99%d7%a8/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-24</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "סוף פואטי" של טוהר קדוש הוא בלדה אפלה על אחיזה נואשת באהבה שכבר איננה  דרך טקסים, פנטזיות ופולחן רגשי. העיבוד האלקטרוני העדין, בקצב מיד־טמפו איטי, יוצר תחושת לופ מתמשך גם מוזיקלית וגם נפשית. זו לא דרמה מתפרצת, אלא שחיקה</v>
+        <v>השיר “מאיר” של נדב דלומי הוא שיר צער אישי הנע בין הבטחה לגאולה לבין התפכחות כואבת. זהו מסע כפול – גיאוגרפי ונפשי – מן הבית בעיראק אל ישראל, מן הענן המרחף אל אדמת הטרשים, מן השמש והירח כסמלי אור אל</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>טוהר קדוש – סוף פואטי</v>
+        <v>נדב דלומי – מאיר</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-02-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week04/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נדב דלומי – מאיר</v>
+        <v>הראל ליסמן – אל תדאג</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%93%d7%91-%d7%93%d7%9c%d7%95%d7%9e%d7%99-%d7%9e%d7%90%d7%99%d7%a8/</v>
+        <v>https://yosmusic.com/%d7%94%d7%a8%d7%90%d7%9c-%d7%9c%d7%99%d7%a1%d7%9e%d7%9f-%d7%90%d7%9c-%d7%aa%d7%93%d7%90%d7%92/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר “מאיר” של נדב דלומי הוא שיר צער אישי הנע בין הבטחה לגאולה לבין התפכחות כואבת. זהו מסע כפול – גיאוגרפי ונפשי – מן הבית בעיראק אל ישראל, מן הענן המרחף אל אדמת הטרשים, מן השמש והירח כסמלי אור אל</v>
+        <v>“אל תדאג” היא בלדת פופ אמוציונלית הבנויה כווידוי פנימי שמופנה החוצה,  אך למעשה מדבר פנימה. זהו שיר שנכתב מתוך עייפות שקטה: לא קריסה דרמטית, אלא שחיקה מתמשכת של מי שמורגל לבקש אישור, להחזיק תדמית יציבה וחזקה, ובתוך כך לנהל מאבק</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נדב דלומי – מאיר</v>
+        <v>הראל ליסמן – אל תדאג</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-02-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>הראל ליסמן – אל תדאג</v>
+        <v>יאיר שלום - מחרוזת מורל 2026</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-25</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%a8%d7%90%d7%9c-%d7%9c%d7%99%d7%a1%d7%9e%d7%9f-%d7%90%d7%9c-%d7%aa%d7%93%d7%90%d7%92/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409747&amp;sid=af3c2eecbe0b94b859644598e62e667f</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-25</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>“אל תדאג” היא בלדת פופ אמוציונלית הבנויה כווידוי פנימי שמופנה החוצה,  אך למעשה מדבר פנימה. זהו שיר שנכתב מתוך עייפות שקטה: לא קריסה דרמטית, אלא שחיקה מתמשכת של מי שמורגל לבקש אישור, להחזיק תדמית יציבה וחזקה, ובתוך כך לנהל מאבק</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,316 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>הראל ליסמן – אל תדאג</v>
+        <v>יאיר שלום - מחרוזת מורל 2026</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>זיו אלקיים - לא הכרתי את עצמי</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-02-25</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409746&amp;sid=af3c2eecbe0b94b859644598e62e667f</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-02-25</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>זיו אלקיים - לא הכרתי את עצמי</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>הראל סבג - ענן של רגשות</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-02-25</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409745&amp;sid=af3c2eecbe0b94b859644598e62e667f</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-02-25</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>הראל סבג - ענן של רגשות</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>אריאל אזולאי - מראה שעל הקיר</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-02-25</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409744&amp;sid=af3c2eecbe0b94b859644598e62e667f</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-02-25</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>אריאל אזולאי - מראה שעל הקיר</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>אבירם שוקרון - מיליון דרכים</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-02-25</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409743&amp;sid=af3c2eecbe0b94b859644598e62e667f</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-02-25</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>אבירם שוקרון - מיליון דרכים</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>אליסף עמר - יאללה</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-02-25</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409742&amp;sid=af3c2eecbe0b94b859644598e62e667f</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-02-25</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>אליסף עמר - יאללה</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>אבי חיימי - שמע אלי</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-02-25</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409741&amp;sid=af3c2eecbe0b94b859644598e62e667f</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-02-25</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>אבי חיימי - שמע אלי</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אבי חיימי - את בדמי</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-02-25</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409740&amp;sid=af3c2eecbe0b94b859644598e62e667f</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-02-25</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אבי חיימי - את בדמי</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>גיא יהוד – חיבוק אחרון</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-02-25</v>
+      </c>
+      <c r="C10" t="str">
+        <v>https://yosmusic.com/%d7%92%d7%99%d7%90-%d7%99%d7%94%d7%95%d7%93-%d7%97%d7%99%d7%91%d7%95%d7%a7-%d7%90%d7%97%d7%a8%d7%95%d7%9f/</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-02-25</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v>“חיבוק אחרון” מבוצע בתפקיד כפול – גיא יהוד מגלם גם את קולה של הדוברת הנשברת וגם את קולו של בן הזוג המנסה להרגיע, להסביר או להיאחז. הבחירה הזו מייצרת דרמה פנימית, כמעט דיאלוג תיאטרלי בתוך שיר פופ ים־תיכוני. השיר נשען</v>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>גיא יהוד – חיבוק אחרון</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-02-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יאיר שלום - מחרוזת מורל 2026</v>
+        <v>ישראל גברא - המלאך שלצידי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-25</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409747&amp;sid=af3c2eecbe0b94b859644598e62e667f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409753&amp;sid=3df3caa326d3485ba1e8650a1e5841a1</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-25</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יאיר שלום - מחרוזת מורל 2026</v>
+        <v>ישראל גברא - המלאך שלצידי</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>זיו אלקיים - לא הכרתי את עצמי</v>
+        <v>רוי סופר - את לא שווה אותי</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-25</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409746&amp;sid=af3c2eecbe0b94b859644598e62e667f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409752&amp;sid=3df3caa326d3485ba1e8650a1e5841a1</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-25</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>זיו אלקיים - לא הכרתי את עצמי</v>
+        <v>רוי סופר - את לא שווה אותי</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>הראל סבג - ענן של רגשות</v>
+        <v>שילה אליה - עבדו</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-25</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409745&amp;sid=af3c2eecbe0b94b859644598e62e667f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409751&amp;sid=3df3caa326d3485ba1e8650a1e5841a1</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-25</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>הראל סבג - ענן של רגשות</v>
+        <v>שילה אליה - עבדו</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>אריאל אזולאי - מראה שעל הקיר</v>
+        <v>שי בסיל - הלב שלי שותק</v>
       </c>
       <c r="B5" t="str">
         <v>2026-02-25</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409744&amp;sid=af3c2eecbe0b94b859644598e62e667f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409750&amp;sid=3df3caa326d3485ba1e8650a1e5841a1</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-25</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>אריאל אזולאי - מראה שעל הקיר</v>
+        <v>שי בסיל - הלב שלי שותק</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>אבירם שוקרון - מיליון דרכים</v>
+        <v>עמיחי אלמו &amp; נביו לגסה - יופי מושלם</v>
       </c>
       <c r="B6" t="str">
         <v>2026-02-25</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409743&amp;sid=af3c2eecbe0b94b859644598e62e667f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409749&amp;sid=3df3caa326d3485ba1e8650a1e5841a1</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-25</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>אבירם שוקרון - מיליון דרכים</v>
+        <v>עמיחי אלמו &amp; נביו לגסה - יופי מושלם</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>אליסף עמר - יאללה</v>
+        <v>ניתאי טויטו - שיר על מזל</v>
       </c>
       <c r="B7" t="str">
         <v>2026-02-25</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409742&amp;sid=af3c2eecbe0b94b859644598e62e667f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409748&amp;sid=3df3caa326d3485ba1e8650a1e5841a1</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-25</v>
@@ -659,126 +659,12 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>אליסף עמר - יאללה</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>אבי חיימי - שמע אלי</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-02-25</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409741&amp;sid=af3c2eecbe0b94b859644598e62e667f</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-02-25</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>אבי חיימי - שמע אלי</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>אבי חיימי - את בדמי</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-02-25</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409740&amp;sid=af3c2eecbe0b94b859644598e62e667f</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-02-25</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>אבי חיימי - את בדמי</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>גיא יהוד – חיבוק אחרון</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-02-25</v>
-      </c>
-      <c r="C10" t="str">
-        <v>https://yosmusic.com/%d7%92%d7%99%d7%90-%d7%99%d7%94%d7%95%d7%93-%d7%97%d7%99%d7%91%d7%95%d7%a7-%d7%90%d7%97%d7%a8%d7%95%d7%9f/</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-02-25</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v>“חיבוק אחרון” מבוצע בתפקיד כפול – גיא יהוד מגלם גם את קולה של הדוברת הנשברת וגם את קולו של בן הזוג המנסה להרגיע, להסביר או להיאחז. הבחירה הזו מייצרת דרמה פנימית, כמעט דיאלוג תיאטרלי בתוך שיר פופ ים־תיכוני. השיר נשען</v>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>גיא יהוד – חיבוק אחרון</v>
+        <v>ניתאי טויטו - שיר על מזל</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-02-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ישראל גברא - המלאך שלצידי</v>
+        <v>אמיר דדון – רחובות ריקים</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409753&amp;sid=3df3caa326d3485ba1e8650a1e5841a1</v>
+        <v>https://yosmusic.com/%d7%90%d7%9e%d7%99%d7%a8-%d7%93%d7%93%d7%95%d7%9f-%d7%a8%d7%97%d7%95%d7%91%d7%95%d7%aa-%d7%a8%d7%99%d7%a7%d7%99%d7%9d/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>אמיר דדון בנה לעצמו לאורך השנים זהות של זמר-מספר: קול עמוק, מחוספס אך נקי, שמחזיק שירים פשוטים ומטעין אותם במשקל רגשי כבד. “רחובות ריקים” הוא דוגמה מובהקת לאופן שבו בלדת אהבה לכאורה מינימלית הופכת בידיים הנכונות לאמירה עוצמתית וכנה. השיר</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,202 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ישראל גברא - המלאך שלצידי</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>רוי סופר - את לא שווה אותי</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-02-25</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409752&amp;sid=3df3caa326d3485ba1e8650a1e5841a1</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-02-25</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>רוי סופר - את לא שווה אותי</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>שילה אליה - עבדו</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-02-25</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409751&amp;sid=3df3caa326d3485ba1e8650a1e5841a1</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-02-25</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>שילה אליה - עבדו</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>שי בסיל - הלב שלי שותק</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-02-25</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409750&amp;sid=3df3caa326d3485ba1e8650a1e5841a1</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-02-25</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>שי בסיל - הלב שלי שותק</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>עמיחי אלמו &amp; נביו לגסה - יופי מושלם</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-02-25</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409749&amp;sid=3df3caa326d3485ba1e8650a1e5841a1</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-02-25</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>עמיחי אלמו &amp; נביו לגסה - יופי מושלם</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>ניתאי טויטו - שיר על מזל</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-02-25</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409748&amp;sid=3df3caa326d3485ba1e8650a1e5841a1</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-02-25</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>ניתאי טויטו - שיר על מזל</v>
+        <v>אמיר דדון – רחובות ריקים</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-02-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אמיר דדון – רחובות ריקים</v>
+        <v>שרון הולצמן – מחמיץ</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-26</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%9e%d7%99%d7%a8-%d7%93%d7%93%d7%95%d7%9f-%d7%a8%d7%97%d7%95%d7%91%d7%95%d7%aa-%d7%a8%d7%99%d7%a7%d7%99%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%a9%d7%a8%d7%95%d7%9f-%d7%94%d7%95%d7%9c%d7%a6%d7%9e%d7%9f-%d7%9e%d7%97%d7%9e%d7%99%d7%a5/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-26</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>אמיר דדון בנה לעצמו לאורך השנים זהות של זמר-מספר: קול עמוק, מחוספס אך נקי, שמחזיק שירים פשוטים ומטעין אותם במשקל רגשי כבד. “רחובות ריקים” הוא דוגמה מובהקת לאופן שבו בלדת אהבה לכאורה מינימלית הופכת בידיים הנכונות לאמירה עוצמתית וכנה. השיר</v>
+        <v>“מחמיץ” ששר שרון הולצמן בזחיחות דעת, הוא שיר שנשמע תחילה כמו בדיחה קטנה על קנאה חברתית,  אבל בהאזנה עמוקה מתגלה כטקסט ציני, חתרני ואפילו פוליטי במסווה של הומור יבש. הוא מתבסס על פעלול הכפילות הלשונית: להחמיץ = לפספס, להחמיץ =</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אמיר דדון – רחובות ריקים</v>
+        <v>שרון הולצמן – מחמיץ</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-02-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L18"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שרון הולצמן – מחמיץ</v>
+        <v>מתנאל אסייג - דמי</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%a8%d7%95%d7%9f-%d7%94%d7%95%d7%9c%d7%a6%d7%9e%d7%9f-%d7%9e%d7%97%d7%9e%d7%99%d7%a5/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409805&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>“מחמיץ” ששר שרון הולצמן בזחיחות דעת, הוא שיר שנשמע תחילה כמו בדיחה קטנה על קנאה חברתית,  אבל בהאזנה עמוקה מתגלה כטקסט ציני, חתרני ואפילו פוליטי במסווה של הומור יבש. הוא מתבסס על פעלול הכפילות הלשונית: להחמיץ = לפספס, להחמיץ =</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,620 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שרון הולצמן – מחמיץ</v>
+        <v>מתנאל אסייג - דמי</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>מוני נחמני - מחרוזת דיכאון 2026</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409804&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>מוני נחמני - מחרוזת דיכאון 2026</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>מאור נוף - מחרוזת תמיד אוהב אותי 2026</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409803&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>מאור נוף - מחרוזת תמיד אוהב אותי 2026</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>ישראל כהן - רואה בי את האור</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409802&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>ישראל כהן - רואה בי את האור</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>ליאור רדעי - בחורה מטורפת</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409801&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>ליאור רדעי - בחורה מטורפת</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>לירן אלמוג - זה אני</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409800&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>לירן אלמוג - זה אני</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>ינון בר ששת - מי את באמת</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409794&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>ינון בר ששת - מי את באמת</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>ינון אברהמי - רבי עקיבא</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409793&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>ינון אברהמי - רבי עקיבא</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>חנוך שובל - מחרוזת המדינות 2026</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409792&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>חנוך שובל - מחרוזת המדינות 2026</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>הנסיך מהמזרח - מחרוזת דיכאון חלק ד 2026</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409791&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>הנסיך מהמזרח - מחרוזת דיכאון חלק ד 2026</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>היוצרים - לא פוגעים בלב של גבר</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409790&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>היוצרים - לא פוגעים בלב של גבר</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>הנסיך מהמזרח - מחרוזת דיכאון חלק ג 2026</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409789&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>הנסיך מהמזרח - מחרוזת דיכאון חלק ג 2026</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>גיא יהוד - חיבוק אחרון</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409788&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>גיא יהוד - חיבוק אחרון</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>בתאל סבח - זרוק על הבר</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409787&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>בתאל סבח - זרוק על הבר</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>אמיר עוזיאל - איך ממשיכים</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="C16" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409786&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>אמיר עוזיאל - איך ממשיכים</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>אמיר דדון - רחובות ריקים</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="C17" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409785&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v>אמיר דדון - רחובות ריקים</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>אבי חיימי - נתתי לה</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="C18" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409784&amp;sid=4283eb838b5abccd27be1e003e270fd8</v>
+      </c>
+      <c r="D18" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v>אבי חיימי - נתתי לה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L18"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-02-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Romi – תביטי בך</v>
+        <v>בן שוקרון – נותן לזה ללכת</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/romi-%d7%aa%d7%91%d7%99%d7%98%d7%99-%d7%91%d7%9a/</v>
+        <v>https://yosmusic.com/%d7%91%d7%9f-%d7%a9%d7%95%d7%a7%d7%a8%d7%95%d7%9f-%d7%a0%d7%95%d7%aa%d7%9f-%d7%9c%d7%96%d7%94-%d7%9c%d7%9c%d7%9b%d7%aa/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-28</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>“תביטי בך” של רומי אטון הוא שיר של מהלך מוזיקלי ורגשי מעניין : הוא מתחיל כהתכנסות פנימית כמעט מדיטטיבית, ואז מחליף שני הילוכים לפזמון בתנועת סמבה-סווינג מפתיעה, כמעט מנוגדת למה שנאמר במילים. הבתים בנויים סביב תחושת עומס מודרני: “למצוא אותי</v>
+        <v>זהו שיר שממוקם בבירור בתוך גל היצירה הישראלי שאחרי השבעה באוקטובר לא כשיר זיכרון לאומי ישיר, אלא כעדות פנימית, כמעט טיפולית, של אדם המתמודד עם פוסט־טראומה. בניגוד לשירי אבל דרמטיים, כאן הבחירה של בן שוקרון היא בתהליך של שיקום איטי.</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Romi – תביטי בך</v>
+        <v>בן שוקרון – נותן לזה ללכת</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-02-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>בן שוקרון – נותן לזה ללכת</v>
+        <v>קלימה - אני חוזר אליך</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-28</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%91%d7%9f-%d7%a9%d7%95%d7%a7%d7%a8%d7%95%d7%9f-%d7%a0%d7%95%d7%aa%d7%9f-%d7%9c%d7%96%d7%94-%d7%9c%d7%9c%d7%9b%d7%aa/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409813&amp;sid=6e0b8078f30a53230379063b56e27b19</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-28</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>זהו שיר שממוקם בבירור בתוך גל היצירה הישראלי שאחרי השבעה באוקטובר לא כשיר זיכרון לאומי ישיר, אלא כעדות פנימית, כמעט טיפולית, של אדם המתמודד עם פוסט־טראומה. בניגוד לשירי אבל דרמטיים, כאן הבחירה של בן שוקרון היא בתהליך של שיקום איטי.</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,240 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>בן שוקרון – נותן לזה ללכת</v>
+        <v>קלימה - אני חוזר אליך</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>ערן סופר - מחרוזת פזמונים 2026</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-02-28</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409812&amp;sid=6e0b8078f30a53230379063b56e27b19</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-02-28</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>ערן סופר - מחרוזת פזמונים 2026</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>פארידה - מתוך החושך</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-02-28</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409811&amp;sid=6e0b8078f30a53230379063b56e27b19</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-02-28</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>פארידה - מתוך החושך</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>עידן כהן - הסיבה לחיות</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-02-28</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409810&amp;sid=6e0b8078f30a53230379063b56e27b19</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-02-28</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>עידן כהן - הסיבה לחיות</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>עידן דבי - מטוסים עפים</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-02-28</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409809&amp;sid=6e0b8078f30a53230379063b56e27b19</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-02-28</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>עידן דבי - מטוסים עפים</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>עידן דבי - ביטים עצובים</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-02-28</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409808&amp;sid=6e0b8078f30a53230379063b56e27b19</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-02-28</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>עידן דבי - ביטים עצובים</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>נועה אבוהב - מקלט לאוהבים</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-02-28</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409807&amp;sid=6e0b8078f30a53230379063b56e27b19</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-02-28</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>נועה אבוהב - מקלט לאוהבים</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-02-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>קלימה - אני חוזר אליך</v>
+        <v>נשמה וקצב - נפש תאומה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-28</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409813&amp;sid=6e0b8078f30a53230379063b56e27b19</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409825&amp;sid=55891609511621b1adecc708f3015fa1</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-28</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>קלימה - אני חוזר אליך</v>
+        <v>נשמה וקצב - נפש תאומה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ערן סופר - מחרוזת פזמונים 2026</v>
+        <v>נוה גדג׳ &amp; בלאדי מורי - כל יום כמו חדש</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-28</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409812&amp;sid=6e0b8078f30a53230379063b56e27b19</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409824&amp;sid=55891609511621b1adecc708f3015fa1</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-28</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>ערן סופר - מחרוזת פזמונים 2026</v>
+        <v>נוה גדג׳ &amp; בלאדי מורי - כל יום כמו חדש</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>פארידה - מתוך החושך</v>
+        <v>לירון טובול - מרשמלו</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-28</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409811&amp;sid=6e0b8078f30a53230379063b56e27b19</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409823&amp;sid=55891609511621b1adecc708f3015fa1</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-28</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>פארידה - מתוך החושך</v>
+        <v>לירון טובול - מרשמלו</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>עידן כהן - הסיבה לחיות</v>
+        <v>ליאל בריל - קמילו - גרסה אקוסטית</v>
       </c>
       <c r="B5" t="str">
         <v>2026-02-28</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409810&amp;sid=6e0b8078f30a53230379063b56e27b19</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409822&amp;sid=55891609511621b1adecc708f3015fa1</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-28</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>עידן כהן - הסיבה לחיות</v>
+        <v>ליאל בריל - קמילו - גרסה אקוסטית</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>עידן דבי - מטוסים עפים</v>
+        <v>להקת דרך - שואל לאן</v>
       </c>
       <c r="B6" t="str">
         <v>2026-02-28</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409809&amp;sid=6e0b8078f30a53230379063b56e27b19</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409821&amp;sid=55891609511621b1adecc708f3015fa1</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-28</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>עידן דבי - מטוסים עפים</v>
+        <v>להקת דרך - שואל לאן</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>עידן דבי - ביטים עצובים</v>
+        <v>הרב יהושע מרגלית - מחרוזת פורים 2026</v>
       </c>
       <c r="B7" t="str">
         <v>2026-02-28</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409808&amp;sid=6e0b8078f30a53230379063b56e27b19</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409820&amp;sid=55891609511621b1adecc708f3015fa1</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-28</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>עידן דבי - ביטים עצובים</v>
+        <v>הרב יהושע מרגלית - מחרוזת פורים 2026</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>נועה אבוהב - מקלט לאוהבים</v>
+        <v>החללית &amp; אבי אבורומי &amp; עידן בקשי - אהבה של כאב</v>
       </c>
       <c r="B8" t="str">
         <v>2026-02-28</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409807&amp;sid=6e0b8078f30a53230379063b56e27b19</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409819&amp;sid=55891609511621b1adecc708f3015fa1</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-28</v>
@@ -697,12 +697,202 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>נועה אבוהב - מקלט לאוהבים</v>
+        <v>החללית &amp; אבי אבורומי &amp; עידן בקשי - אהבה של כאב</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>ג'וני נאפש &amp; צוף מימון - לפני שנכנסת לתמונה</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-02-28</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409818&amp;sid=55891609511621b1adecc708f3015fa1</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-02-28</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>ג'וני נאפש &amp; צוף מימון - לפני שנכנסת לתמונה</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>בניסים - לילות לבנים</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-02-28</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409817&amp;sid=55891609511621b1adecc708f3015fa1</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-02-28</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>בניסים - לילות לבנים</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אליה נרקיס - שתיים בלילה</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-02-28</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409816&amp;sid=55891609511621b1adecc708f3015fa1</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-02-28</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אליה נרקיס - שתיים בלילה</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>אייר זינגר - מזמור לתודה</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-02-28</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409815&amp;sid=55891609511621b1adecc708f3015fa1</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-02-28</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>אייר זינגר - מזמור לתודה</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>אברהם יצחק - מטאור</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-02-28</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409814&amp;sid=55891609511621b1adecc708f3015fa1</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-02-28</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>אברהם יצחק - מטאור</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L13"/>
   </ignoredErrors>
 </worksheet>
 </file>